--- a/AMS/006-Diago/Diago_Financials_FY_2025-2026_V5.xlsx
+++ b/AMS/006-Diago/Diago_Financials_FY_2025-2026_V5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\AMS\006-Diago\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3948D036-31B2-42B2-8BE2-4DB4920969E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89278D8B-3D79-47F2-9E45-BB256C93058F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -2145,21 +2145,66 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2172,9 +2217,6 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2187,9 +2229,6 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2199,36 +2238,6 @@
     <xf numFmtId="43" fontId="2" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2270,15 +2279,6 @@
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2585,43 +2585,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="184" t="s">
         <v>296</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="171"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="186"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="187" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="174"/>
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="188"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="172" t="s">
+      <c r="A3" s="187" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="176"/>
+      <c r="B3" s="189"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="189"/>
+      <c r="F3" s="189"/>
+      <c r="G3" s="189"/>
+      <c r="H3" s="190"/>
     </row>
     <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="177" t="s">
+      <c r="A4" s="191" t="s">
         <v>248</v>
       </c>
       <c r="B4" s="178"/>
@@ -2630,16 +2630,16 @@
       <c r="E4" s="178"/>
       <c r="F4" s="178"/>
       <c r="G4" s="178"/>
-      <c r="H4" s="179"/>
+      <c r="H4" s="192"/>
     </row>
     <row r="5" spans="1:8" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="83" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="180" t="s">
+      <c r="B5" s="193" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="181"/>
+      <c r="C5" s="194"/>
       <c r="D5" s="94" t="s">
         <v>231</v>
       </c>
@@ -2647,10 +2647,10 @@
         <f>+A5</f>
         <v>March 31, 2025</v>
       </c>
-      <c r="F5" s="180" t="s">
+      <c r="F5" s="193" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="181"/>
+      <c r="G5" s="194"/>
       <c r="H5" s="83" t="str">
         <f>+D5</f>
         <v>March 31, 2026</v>
@@ -2808,10 +2808,10 @@
       <c r="E14" s="85">
         <v>1228170</v>
       </c>
-      <c r="F14" s="206" t="s">
+      <c r="F14" s="164" t="s">
         <v>125</v>
       </c>
-      <c r="G14" s="207">
+      <c r="G14" s="165">
         <f>'FD Sch_2'!D81</f>
         <v>1523053</v>
       </c>
@@ -2827,7 +2827,7 @@
       <c r="E15" s="85">
         <v>67712</v>
       </c>
-      <c r="F15" s="208" t="s">
+      <c r="F15" s="166" t="s">
         <v>4</v>
       </c>
       <c r="G15" s="118">
@@ -3195,10 +3195,10 @@
         <f>SUM(A10:A34)</f>
         <v>3918781.46</v>
       </c>
-      <c r="B35" s="168" t="s">
+      <c r="B35" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="168"/>
+      <c r="C35" s="181"/>
       <c r="D35" s="92">
         <f>SUM(D10:D34)</f>
         <v>4162010.46</v>
@@ -3207,10 +3207,10 @@
         <f>SUM(E6:E34)</f>
         <v>3918781.46</v>
       </c>
-      <c r="F35" s="168" t="s">
+      <c r="F35" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="G35" s="168"/>
+      <c r="G35" s="181"/>
       <c r="H35" s="82">
         <f>SUM(H6:H34)</f>
         <v>4162010.46</v>
@@ -3238,12 +3238,12 @@
       <c r="B37" s="66"/>
       <c r="C37" s="67"/>
       <c r="D37" s="66"/>
-      <c r="E37" s="166" t="s">
+      <c r="E37" s="169" t="s">
         <v>297</v>
       </c>
-      <c r="F37" s="166"/>
-      <c r="G37" s="166"/>
-      <c r="H37" s="167"/>
+      <c r="F37" s="169"/>
+      <c r="G37" s="169"/>
+      <c r="H37" s="183"/>
       <c r="I37" s="67"/>
       <c r="J37" s="66"/>
       <c r="K37" s="66"/>
@@ -3289,12 +3289,12 @@
       </c>
       <c r="B42" s="75"/>
       <c r="C42" s="76"/>
-      <c r="E42" s="166" t="s">
+      <c r="E42" s="169" t="s">
         <v>294</v>
       </c>
-      <c r="F42" s="166"/>
-      <c r="G42" s="166"/>
-      <c r="H42" s="167"/>
+      <c r="F42" s="169"/>
+      <c r="G42" s="169"/>
+      <c r="H42" s="183"/>
       <c r="I42" s="67"/>
     </row>
     <row r="43" spans="1:13" s="66" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
@@ -3310,11 +3310,11 @@
       <c r="I43" s="67"/>
     </row>
     <row r="44" spans="1:13" s="66" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A44" s="164">
+      <c r="A44" s="182">
         <v>46221</v>
       </c>
-      <c r="B44" s="165"/>
-      <c r="C44" s="165"/>
+      <c r="B44" s="168"/>
+      <c r="C44" s="168"/>
       <c r="H44" s="71"/>
       <c r="I44" s="67"/>
     </row>
@@ -3368,46 +3368,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="str">
+      <c r="A1" s="171" t="str">
         <f>BS!A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="186"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="173"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="187" t="str">
+      <c r="A2" s="174" t="str">
         <f>BS!A2</f>
         <v>186-A, Baudi Cross Lane, Orlem, Malad (West), Mumbai, Maharashtra - 400064</v>
       </c>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="188"/>
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="176"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="187" t="str">
+      <c r="A3" s="174" t="str">
         <f>BS!A3</f>
         <v>Society Reg No : BOM/(WP)/HSG(TC) 1007/84-85 dated.13/07/1984</v>
       </c>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="188"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="176"/>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="189" t="s">
+      <c r="A4" s="177" t="s">
         <v>230</v>
       </c>
       <c r="B4" s="178"/>
@@ -3416,16 +3416,16 @@
       <c r="E4" s="178"/>
       <c r="F4" s="178"/>
       <c r="G4" s="178"/>
-      <c r="H4" s="190"/>
+      <c r="H4" s="179"/>
     </row>
     <row r="5" spans="1:10" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="97" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="191" t="s">
+      <c r="B5" s="180" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="191"/>
+      <c r="C5" s="180"/>
       <c r="D5" s="87" t="s">
         <v>231</v>
       </c>
@@ -3433,10 +3433,10 @@
         <f>+A5</f>
         <v>March 31, 2025</v>
       </c>
-      <c r="F5" s="191" t="s">
+      <c r="F5" s="180" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="191"/>
+      <c r="G5" s="180"/>
       <c r="H5" s="98" t="str">
         <f>+D5</f>
         <v>March 31, 2026</v>
@@ -4257,10 +4257,10 @@
         <f>SUM(A6:A51)</f>
         <v>517077</v>
       </c>
-      <c r="B52" s="168" t="s">
+      <c r="B52" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="168"/>
+      <c r="C52" s="181"/>
       <c r="D52" s="92">
         <f>SUM(D6:D51)</f>
         <v>531563</v>
@@ -4269,10 +4269,10 @@
         <f>SUM(E6:E51)</f>
         <v>517077</v>
       </c>
-      <c r="F52" s="168" t="s">
+      <c r="F52" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="G52" s="168"/>
+      <c r="G52" s="181"/>
       <c r="H52" s="100">
         <f>SUM(H6:H51)</f>
         <v>531563</v>
@@ -4301,12 +4301,12 @@
       <c r="B54" s="66"/>
       <c r="C54" s="67"/>
       <c r="D54" s="66"/>
-      <c r="E54" s="166" t="s">
+      <c r="E54" s="169" t="s">
         <v>297</v>
       </c>
-      <c r="F54" s="166"/>
-      <c r="G54" s="166"/>
-      <c r="H54" s="183"/>
+      <c r="F54" s="169"/>
+      <c r="G54" s="169"/>
+      <c r="H54" s="170"/>
     </row>
     <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="104"/>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="B59" s="75"/>
       <c r="C59" s="76"/>
-      <c r="E59" s="166" t="s">
+      <c r="E59" s="169" t="s">
         <v>294</v>
       </c>
-      <c r="F59" s="166"/>
-      <c r="G59" s="166"/>
-      <c r="H59" s="183"/>
+      <c r="F59" s="169"/>
+      <c r="G59" s="169"/>
+      <c r="H59" s="170"/>
       <c r="I59" s="67"/>
     </row>
     <row r="60" spans="1:13" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4383,11 +4383,11 @@
       <c r="I60" s="67"/>
     </row>
     <row r="61" spans="1:13" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="182">
+      <c r="A61" s="167">
         <v>46221</v>
       </c>
-      <c r="B61" s="165"/>
-      <c r="C61" s="165"/>
+      <c r="B61" s="168"/>
+      <c r="C61" s="168"/>
       <c r="H61" s="105"/>
       <c r="I61" s="67"/>
     </row>
@@ -4484,20 +4484,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="184" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="171"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="186"/>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="192" t="s">
+      <c r="A2" s="195" t="s">
         <v>238</v>
       </c>
-      <c r="B2" s="193"/>
-      <c r="C2" s="193"/>
-      <c r="D2" s="194"/>
+      <c r="B2" s="196"/>
+      <c r="C2" s="196"/>
+      <c r="D2" s="197"/>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="114" t="s">
@@ -5113,37 +5113,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="195" t="str">
+      <c r="A1" s="198" t="str">
         <f>BS!A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="196"/>
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+      <c r="L1" s="199"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="197" t="s">
+      <c r="A2" s="200" t="s">
         <v>269</v>
       </c>
-      <c r="B2" s="197"/>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="197"/>
-      <c r="G2" s="197"/>
-      <c r="H2" s="197"/>
-      <c r="I2" s="197"/>
-      <c r="J2" s="197"/>
-      <c r="K2" s="197"/>
-      <c r="L2" s="197"/>
+      <c r="B2" s="200"/>
+      <c r="C2" s="200"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="200"/>
+      <c r="H2" s="200"/>
+      <c r="I2" s="200"/>
+      <c r="J2" s="200"/>
+      <c r="K2" s="200"/>
+      <c r="L2" s="200"/>
     </row>
     <row r="3" spans="1:14" s="27" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
@@ -5526,7 +5526,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="29" t="s">
         <v>219</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="29" t="s">
         <v>208</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="29" t="s">
         <v>262</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>254</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" s="56" t="s">
         <v>278</v>
@@ -5781,7 +5781,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" s="56" t="s">
         <v>251</v>
@@ -5822,7 +5822,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="56" t="s">
         <v>253</v>
@@ -5863,7 +5863,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="56" t="s">
         <v>210</v>
@@ -5905,7 +5905,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" s="56" t="s">
         <v>258</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="56" t="s">
         <v>261</v>
@@ -5987,7 +5987,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" s="56" t="s">
         <v>264</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28" s="29" t="s">
         <v>220</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" s="29" t="s">
         <v>280</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" s="29" t="s">
         <v>196</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B33" s="29" t="s">
         <v>197</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B34" s="29" t="s">
         <v>198</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" s="29" t="s">
         <v>211</v>
@@ -6410,7 +6410,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B38" s="29" t="s">
         <v>222</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B39" s="29" t="s">
         <v>223</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B42" s="29" t="s">
         <v>199</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" s="29" t="s">
         <v>169</v>
@@ -6617,7 +6617,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B44" s="29" t="s">
         <v>168</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B47" s="29" t="s">
         <v>200</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" s="29" t="s">
         <v>201</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" s="29" t="s">
         <v>202</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B50" s="29" t="s">
         <v>203</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B51" s="29" t="s">
         <v>257</v>
@@ -6911,7 +6911,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B52" s="29" t="s">
         <v>265</v>
@@ -6984,37 +6984,37 @@
       <c r="O53" s="30"/>
     </row>
     <row r="54" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A54" s="195" t="str">
+      <c r="A54" s="198" t="str">
         <f>+A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B54" s="196"/>
-      <c r="C54" s="196"/>
-      <c r="D54" s="196"/>
-      <c r="E54" s="196"/>
-      <c r="F54" s="196"/>
-      <c r="G54" s="196"/>
-      <c r="H54" s="196"/>
-      <c r="I54" s="196"/>
-      <c r="J54" s="196"/>
-      <c r="K54" s="196"/>
-      <c r="L54" s="196"/>
+      <c r="B54" s="199"/>
+      <c r="C54" s="199"/>
+      <c r="D54" s="199"/>
+      <c r="E54" s="199"/>
+      <c r="F54" s="199"/>
+      <c r="G54" s="199"/>
+      <c r="H54" s="199"/>
+      <c r="I54" s="199"/>
+      <c r="J54" s="199"/>
+      <c r="K54" s="199"/>
+      <c r="L54" s="199"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="197" t="s">
+      <c r="A55" s="200" t="s">
         <v>269</v>
       </c>
-      <c r="B55" s="197"/>
-      <c r="C55" s="197"/>
-      <c r="D55" s="197"/>
-      <c r="E55" s="197"/>
-      <c r="F55" s="197"/>
-      <c r="G55" s="197"/>
-      <c r="H55" s="197"/>
-      <c r="I55" s="197"/>
-      <c r="J55" s="197"/>
-      <c r="K55" s="197"/>
-      <c r="L55" s="197"/>
+      <c r="B55" s="200"/>
+      <c r="C55" s="200"/>
+      <c r="D55" s="200"/>
+      <c r="E55" s="200"/>
+      <c r="F55" s="200"/>
+      <c r="G55" s="200"/>
+      <c r="H55" s="200"/>
+      <c r="I55" s="200"/>
+      <c r="J55" s="200"/>
+      <c r="K55" s="200"/>
+      <c r="L55" s="200"/>
     </row>
     <row r="56" spans="1:15" s="27" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="26" t="s">
@@ -7067,7 +7067,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B58" s="29" t="s">
         <v>149</v>
@@ -7107,7 +7107,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59" s="29" t="s">
         <v>204</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="29" t="s">
         <v>205</v>
@@ -7187,7 +7187,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B61" s="29" t="s">
         <v>268</v>
@@ -7271,7 +7271,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B64" s="29" t="s">
         <v>206</v>
@@ -7313,7 +7313,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B65" s="29" t="s">
         <v>170</v>
@@ -7354,7 +7354,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B66" s="29" t="s">
         <v>267</v>
@@ -7439,7 +7439,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B69" s="29" t="s">
         <v>207</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B70" s="29" t="s">
         <v>171</v>
@@ -7522,7 +7522,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B71" s="29" t="s">
         <v>212</v>
@@ -7564,7 +7564,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B72" s="29" t="s">
         <v>266</v>
@@ -7650,7 +7650,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B75" s="29" t="s">
         <v>256</v>
@@ -7691,7 +7691,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B76" s="29" t="s">
         <v>263</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B79" s="29" t="s">
         <v>259</v>
@@ -7914,29 +7914,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="198" t="str">
+      <c r="A1" s="201" t="str">
         <f>BS!A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
+      <c r="B1" s="202"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
+      <c r="G1" s="202"/>
+      <c r="H1" s="202"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="200" t="s">
+      <c r="A2" s="203" t="s">
         <v>249</v>
       </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
+      <c r="H2" s="203"/>
     </row>
     <row r="3" spans="1:8" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="140" t="s">
@@ -8210,34 +8210,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="205" t="str">
+      <c r="A1" s="208" t="str">
         <f>BS!A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B1" s="205"/>
-      <c r="C1" s="205"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="205"/>
-      <c r="H1" s="205"/>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
+      <c r="B1" s="208"/>
+      <c r="C1" s="208"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="208"/>
+      <c r="I1" s="208"/>
+      <c r="J1" s="208"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="173" t="s">
+      <c r="A2" s="175" t="s">
         <v>244</v>
       </c>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="G2" s="173" t="s">
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="G2" s="175" t="s">
         <v>245</v>
       </c>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
+      <c r="J2" s="175"/>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="154" t="s">
@@ -8299,12 +8299,12 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="202" t="s">
+      <c r="A5" s="205" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="203"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="204"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
       <c r="E5" s="162">
         <f>SUM(E4:E4)</f>
         <v>3982</v>
@@ -8337,13 +8337,13 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="201" t="s">
+      <c r="A7" s="204" t="s">
         <v>246</v>
       </c>
-      <c r="B7" s="201"/>
-      <c r="C7" s="201"/>
-      <c r="D7" s="201"/>
-      <c r="E7" s="201"/>
+      <c r="B7" s="204"/>
+      <c r="C7" s="204"/>
+      <c r="D7" s="204"/>
+      <c r="E7" s="204"/>
       <c r="G7" s="143">
         <v>4</v>
       </c>
@@ -8374,11 +8374,11 @@
       <c r="E8" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="202" t="s">
+      <c r="G8" s="205" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="203"/>
-      <c r="I8" s="204"/>
+      <c r="H8" s="206"/>
+      <c r="I8" s="207"/>
       <c r="J8" s="161">
         <f>SUM(J4:J7)</f>
         <v>33044</v>
@@ -8442,12 +8442,12 @@
       <c r="L11" s="150"/>
     </row>
     <row r="12" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="202" t="s">
+      <c r="A12" s="205" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="203"/>
-      <c r="C12" s="203"/>
-      <c r="D12" s="204"/>
+      <c r="B12" s="206"/>
+      <c r="C12" s="206"/>
+      <c r="D12" s="207"/>
       <c r="E12" s="161">
         <f>SUM(E9:E11)</f>
         <v>21383</v>
@@ -8460,13 +8460,13 @@
       <c r="L13" s="150"/>
     </row>
     <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="201" t="s">
+      <c r="A14" s="204" t="s">
         <v>247</v>
       </c>
-      <c r="B14" s="201"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="201"/>
-      <c r="E14" s="201"/>
+      <c r="B14" s="204"/>
+      <c r="C14" s="204"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="204"/>
       <c r="G14" s="135"/>
       <c r="L14" s="150"/>
     </row>

--- a/AMS/006-Diago/Diago_Financials_FY_2025-2026_V5.xlsx
+++ b/AMS/006-Diago/Diago_Financials_FY_2025-2026_V5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\AMS\006-Diago\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89278D8B-3D79-47F2-9E45-BB256C93058F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B72437E-63A5-4930-A36A-3E5234147968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -388,9 +388,6 @@
     <t>Electricity Expenses</t>
   </si>
   <si>
-    <t>Mrs. Dorothy Fernandes</t>
-  </si>
-  <si>
     <t>Mr. Sydney Joe Lobo</t>
   </si>
   <si>
@@ -953,6 +950,9 @@
   </si>
   <si>
     <t>Add: Excess provision fire fighting System. Writte back</t>
+  </si>
+  <si>
+    <t>Suzie Rupesh Dlima &amp; Rupesh Kaitan Dlima</t>
   </si>
 </sst>
 </file>
@@ -2154,15 +2154,72 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2178,66 +2235,18 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2246,15 +2255,6 @@
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2585,72 +2585,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
-        <v>296</v>
-      </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="186"/>
+      <c r="A1" s="175" t="s">
+        <v>295</v>
+      </c>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="177"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="187" t="s">
+      <c r="A2" s="178" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="175"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="188"/>
+      <c r="B2" s="179"/>
+      <c r="C2" s="179"/>
+      <c r="D2" s="179"/>
+      <c r="E2" s="179"/>
+      <c r="F2" s="179"/>
+      <c r="G2" s="179"/>
+      <c r="H2" s="180"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="187" t="s">
+      <c r="A3" s="178" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="189"/>
-      <c r="C3" s="189"/>
-      <c r="D3" s="189"/>
-      <c r="E3" s="189"/>
-      <c r="F3" s="189"/>
-      <c r="G3" s="189"/>
-      <c r="H3" s="190"/>
+      <c r="B3" s="181"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="181"/>
+      <c r="F3" s="181"/>
+      <c r="G3" s="181"/>
+      <c r="H3" s="182"/>
     </row>
     <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="191" t="s">
-        <v>248</v>
-      </c>
-      <c r="B4" s="178"/>
-      <c r="C4" s="178"/>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="192"/>
+      <c r="A4" s="183" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" s="184"/>
+      <c r="C4" s="184"/>
+      <c r="D4" s="184"/>
+      <c r="E4" s="184"/>
+      <c r="F4" s="184"/>
+      <c r="G4" s="184"/>
+      <c r="H4" s="185"/>
     </row>
     <row r="5" spans="1:8" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="83" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="193" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="186" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="194"/>
+      <c r="C5" s="187"/>
       <c r="D5" s="94" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E5" s="84" t="str">
         <f>+A5</f>
         <v>March 31, 2025</v>
       </c>
-      <c r="F5" s="193" t="s">
+      <c r="F5" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="194"/>
+      <c r="G5" s="187"/>
       <c r="H5" s="83" t="str">
         <f>+D5</f>
         <v>March 31, 2026</v>
@@ -2782,7 +2782,7 @@
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="36"/>
       <c r="B13" s="43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="36"/>
       <c r="D13" s="95">
@@ -2809,7 +2809,7 @@
         <v>1228170</v>
       </c>
       <c r="F14" s="164" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G14" s="165">
         <f>'FD Sch_2'!D81</f>
@@ -2862,7 +2862,7 @@
       <c r="D17" s="95"/>
       <c r="E17" s="93"/>
       <c r="F17" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G17" s="36"/>
       <c r="H17" s="35"/>
@@ -2890,7 +2890,7 @@
         <v>31930</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C19" s="36">
         <f>'Advance n Refundable Sch 4 to 7'!E12</f>
@@ -2916,7 +2916,7 @@
         <v>20000</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="40">
         <f>'Advance n Refundable Sch 4 to 7'!E28</f>
@@ -2950,7 +2950,7 @@
       <c r="D22" s="95"/>
       <c r="E22" s="85"/>
       <c r="F22" s="33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G22" s="36"/>
       <c r="H22" s="35"/>
@@ -2970,7 +2970,7 @@
         <v>6921</v>
       </c>
       <c r="F23" s="43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G23" s="36"/>
       <c r="H23" s="35">
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C25" s="36">
         <v>826</v>
@@ -3007,7 +3007,7 @@
       <c r="D25" s="95"/>
       <c r="E25" s="85"/>
       <c r="F25" s="33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G25" s="36"/>
       <c r="H25" s="35"/>
@@ -3017,7 +3017,7 @@
         <v>5310</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C26" s="36">
         <v>3540</v>
@@ -3039,7 +3039,7 @@
         <v>9694</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C27" s="36">
         <f>'Advance n Refundable Sch 4 to 7'!J8</f>
@@ -3050,7 +3050,7 @@
         <v>9802</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G27" s="48">
         <v>3332</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E28" s="85"/>
       <c r="F28" s="38" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G28" s="34"/>
       <c r="H28" s="35">
@@ -3092,7 +3092,7 @@
         <v>6995</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G29" s="36"/>
       <c r="H29" s="35">
@@ -3125,7 +3125,7 @@
       <c r="D31" s="95"/>
       <c r="E31" s="85"/>
       <c r="F31" s="49" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G31" s="36"/>
       <c r="H31" s="35"/>
@@ -3135,7 +3135,7 @@
         <v>1770</v>
       </c>
       <c r="B32" s="50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C32" s="36">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>2287010</v>
       </c>
       <c r="F32" s="43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G32" s="36"/>
       <c r="H32" s="35">
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="B33" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C33" s="36">
         <v>1300</v>
@@ -3175,7 +3175,7 @@
         <v>30928.719999999739</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C34" s="163">
         <f>-IE!H50</f>
@@ -3195,10 +3195,10 @@
         <f>SUM(A10:A34)</f>
         <v>3918781.46</v>
       </c>
-      <c r="B35" s="181" t="s">
+      <c r="B35" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="181"/>
+      <c r="C35" s="174"/>
       <c r="D35" s="92">
         <f>SUM(D10:D34)</f>
         <v>4162010.46</v>
@@ -3207,10 +3207,10 @@
         <f>SUM(E6:E34)</f>
         <v>3918781.46</v>
       </c>
-      <c r="F35" s="181" t="s">
+      <c r="F35" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="G35" s="181"/>
+      <c r="G35" s="174"/>
       <c r="H35" s="82">
         <f>SUM(H6:H34)</f>
         <v>4162010.46</v>
@@ -3233,17 +3233,17 @@
     </row>
     <row r="37" spans="1:13" s="69" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A37" s="65" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B37" s="66"/>
       <c r="C37" s="67"/>
       <c r="D37" s="66"/>
-      <c r="E37" s="169" t="s">
-        <v>297</v>
-      </c>
-      <c r="F37" s="169"/>
-      <c r="G37" s="169"/>
-      <c r="H37" s="183"/>
+      <c r="E37" s="172" t="s">
+        <v>296</v>
+      </c>
+      <c r="F37" s="172"/>
+      <c r="G37" s="172"/>
+      <c r="H37" s="173"/>
       <c r="I37" s="67"/>
       <c r="J37" s="66"/>
       <c r="K37" s="66"/>
@@ -3274,7 +3274,7 @@
     </row>
     <row r="41" spans="1:13" s="66" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B41" s="75"/>
       <c r="C41" s="76"/>
@@ -3285,21 +3285,21 @@
     </row>
     <row r="42" spans="1:13" s="66" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A42" s="77" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B42" s="75"/>
       <c r="C42" s="76"/>
-      <c r="E42" s="169" t="s">
-        <v>294</v>
-      </c>
-      <c r="F42" s="169"/>
-      <c r="G42" s="169"/>
-      <c r="H42" s="183"/>
+      <c r="E42" s="172" t="s">
+        <v>293</v>
+      </c>
+      <c r="F42" s="172"/>
+      <c r="G42" s="172"/>
+      <c r="H42" s="173"/>
       <c r="I42" s="67"/>
     </row>
     <row r="43" spans="1:13" s="66" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A43" s="77" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B43" s="75"/>
       <c r="C43" s="76"/>
@@ -3310,11 +3310,11 @@
       <c r="I43" s="67"/>
     </row>
     <row r="44" spans="1:13" s="66" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A44" s="182">
-        <v>46221</v>
-      </c>
-      <c r="B44" s="168"/>
-      <c r="C44" s="168"/>
+      <c r="A44" s="170">
+        <v>46234</v>
+      </c>
+      <c r="B44" s="171"/>
+      <c r="C44" s="171"/>
       <c r="H44" s="71"/>
       <c r="I44" s="67"/>
     </row>
@@ -3368,75 +3368,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="171" t="str">
+      <c r="A1" s="190" t="str">
         <f>BS!A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="173"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="191"/>
+      <c r="G1" s="191"/>
+      <c r="H1" s="192"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="174" t="str">
+      <c r="A2" s="193" t="str">
         <f>BS!A2</f>
         <v>186-A, Baudi Cross Lane, Orlem, Malad (West), Mumbai, Maharashtra - 400064</v>
       </c>
-      <c r="B2" s="175"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="176"/>
+      <c r="B2" s="179"/>
+      <c r="C2" s="179"/>
+      <c r="D2" s="179"/>
+      <c r="E2" s="179"/>
+      <c r="F2" s="179"/>
+      <c r="G2" s="179"/>
+      <c r="H2" s="194"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="174" t="str">
+      <c r="A3" s="193" t="str">
         <f>BS!A3</f>
         <v>Society Reg No : BOM/(WP)/HSG(TC) 1007/84-85 dated.13/07/1984</v>
       </c>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="176"/>
+      <c r="B3" s="179"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="179"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="194"/>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="177" t="s">
-        <v>230</v>
-      </c>
-      <c r="B4" s="178"/>
-      <c r="C4" s="178"/>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="179"/>
+      <c r="A4" s="195" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4" s="184"/>
+      <c r="C4" s="184"/>
+      <c r="D4" s="184"/>
+      <c r="E4" s="184"/>
+      <c r="F4" s="184"/>
+      <c r="G4" s="184"/>
+      <c r="H4" s="196"/>
     </row>
     <row r="5" spans="1:10" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="97" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="180" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="197" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="180"/>
+      <c r="C5" s="197"/>
       <c r="D5" s="87" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E5" s="58" t="str">
         <f>+A5</f>
         <v>March 31, 2025</v>
       </c>
-      <c r="F5" s="180" t="s">
+      <c r="F5" s="197" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="180"/>
+      <c r="G5" s="197"/>
       <c r="H5" s="98" t="str">
         <f>+D5</f>
         <v>March 31, 2026</v>
@@ -3657,7 +3657,7 @@
         <v>2925</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G16" s="40">
         <v>250</v>
@@ -3706,7 +3706,7 @@
         <v>2510</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C19" s="47">
         <v>3304</v>
@@ -3728,7 +3728,7 @@
         <v>1300</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C20" s="36">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>751</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G20" s="36">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C21" s="54">
         <v>18000</v>
@@ -3819,7 +3819,7 @@
         <v>7</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G24" s="36">
         <v>0</v>
@@ -3964,7 +3964,7 @@
         <v>2500</v>
       </c>
       <c r="B33" s="41" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C33" s="47">
         <v>12000</v>
@@ -3996,7 +3996,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C35" s="36">
         <v>674</v>
@@ -4012,7 +4012,7 @@
         <v>3000</v>
       </c>
       <c r="B36" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C36" s="36">
         <v>0</v>
@@ -4028,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="41" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C37" s="54">
         <v>99</v>
@@ -4055,7 +4055,7 @@
     <row r="39" spans="1:8" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="39"/>
       <c r="B39" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C39" s="36"/>
       <c r="D39" s="88"/>
@@ -4166,7 +4166,7 @@
         <v>10095</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C46" s="10">
         <v>10760</v>
@@ -4182,7 +4182,7 @@
         <v>2205</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C47" s="40">
         <v>2760</v>
@@ -4221,13 +4221,13 @@
         <v>10309</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C50" s="36"/>
       <c r="D50" s="91"/>
       <c r="E50" s="85"/>
       <c r="F50" s="45" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G50" s="36"/>
       <c r="H50" s="37">
@@ -4241,7 +4241,7 @@
         <v>30928.719999999972</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C51" s="36">
         <v>0</v>
@@ -4257,10 +4257,10 @@
         <f>SUM(A6:A51)</f>
         <v>517077</v>
       </c>
-      <c r="B52" s="181" t="s">
+      <c r="B52" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="181"/>
+      <c r="C52" s="174"/>
       <c r="D52" s="92">
         <f>SUM(D6:D51)</f>
         <v>531563</v>
@@ -4269,10 +4269,10 @@
         <f>SUM(E6:E51)</f>
         <v>517077</v>
       </c>
-      <c r="F52" s="181" t="s">
+      <c r="F52" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="G52" s="181"/>
+      <c r="G52" s="174"/>
       <c r="H52" s="100">
         <f>SUM(H6:H51)</f>
         <v>531563</v>
@@ -4296,17 +4296,17 @@
     </row>
     <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="103" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B54" s="66"/>
       <c r="C54" s="67"/>
       <c r="D54" s="66"/>
-      <c r="E54" s="169" t="s">
-        <v>297</v>
-      </c>
-      <c r="F54" s="169"/>
-      <c r="G54" s="169"/>
-      <c r="H54" s="170"/>
+      <c r="E54" s="172" t="s">
+        <v>296</v>
+      </c>
+      <c r="F54" s="172"/>
+      <c r="G54" s="172"/>
+      <c r="H54" s="189"/>
     </row>
     <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="104"/>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="58" spans="1:13" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="107" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B58" s="75"/>
       <c r="C58" s="76"/>
@@ -4358,21 +4358,21 @@
     </row>
     <row r="59" spans="1:13" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="108" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B59" s="75"/>
       <c r="C59" s="76"/>
-      <c r="E59" s="169" t="s">
-        <v>294</v>
-      </c>
-      <c r="F59" s="169"/>
-      <c r="G59" s="169"/>
-      <c r="H59" s="170"/>
+      <c r="E59" s="172" t="s">
+        <v>293</v>
+      </c>
+      <c r="F59" s="172"/>
+      <c r="G59" s="172"/>
+      <c r="H59" s="189"/>
       <c r="I59" s="67"/>
     </row>
     <row r="60" spans="1:13" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="108" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B60" s="75"/>
       <c r="C60" s="76"/>
@@ -4383,11 +4383,12 @@
       <c r="I60" s="67"/>
     </row>
     <row r="61" spans="1:13" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="167">
-        <v>46221</v>
-      </c>
-      <c r="B61" s="168"/>
-      <c r="C61" s="168"/>
+      <c r="A61" s="188">
+        <f>+BS!A44</f>
+        <v>46234</v>
+      </c>
+      <c r="B61" s="171"/>
+      <c r="C61" s="171"/>
       <c r="H61" s="105"/>
       <c r="I61" s="67"/>
     </row>
@@ -4484,31 +4485,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="175" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="186"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="177"/>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="195" t="s">
-        <v>238</v>
-      </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
-      <c r="D2" s="197"/>
+      <c r="A2" s="198" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" s="199"/>
+      <c r="C2" s="199"/>
+      <c r="D2" s="200"/>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="114" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B3" s="113" t="s">
         <v>94</v>
       </c>
       <c r="C3" s="115"/>
       <c r="D3" s="116" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -4656,7 +4657,7 @@
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="117"/>
@@ -4890,7 +4891,7 @@
         <v>-9028</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C30" s="10">
         <v>-6470</v>
@@ -5005,7 +5006,7 @@
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="117"/>
@@ -5113,37 +5114,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="198" t="str">
+      <c r="A1" s="167" t="str">
         <f>BS!A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="168"/>
+      <c r="K1" s="168"/>
+      <c r="L1" s="168"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="200" t="s">
-        <v>269</v>
-      </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="200"/>
-      <c r="K2" s="200"/>
-      <c r="L2" s="200"/>
+      <c r="A2" s="169" t="s">
+        <v>268</v>
+      </c>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="169"/>
+      <c r="L2" s="169"/>
     </row>
     <row r="3" spans="1:14" s="27" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
@@ -5159,10 +5160,10 @@
         <v>13</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>63</v>
@@ -5193,10 +5194,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D5" s="11">
         <v>13194</v>
@@ -5218,7 +5219,7 @@
         <v>14335</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J5" s="16">
         <v>16248</v>
@@ -5235,10 +5236,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D6" s="11">
         <v>7366</v>
@@ -5260,7 +5261,7 @@
         <v>8254</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J6" s="16">
         <v>9071</v>
@@ -5277,10 +5278,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D7" s="11">
         <v>7281</v>
@@ -5302,7 +5303,7 @@
         <v>8133</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J7" s="16">
         <v>8966</v>
@@ -5319,10 +5320,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D8" s="11">
         <v>19266</v>
@@ -5344,7 +5345,7 @@
         <v>21531</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J8" s="16">
         <v>23725</v>
@@ -5361,10 +5362,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D9" s="11">
         <v>11492</v>
@@ -5386,7 +5387,7 @@
         <v>12296</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J9" s="16">
         <v>12688</v>
@@ -5403,10 +5404,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D10" s="11">
         <v>26590</v>
@@ -5428,7 +5429,7 @@
         <v>28451</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J10" s="16">
         <v>29358</v>
@@ -5445,10 +5446,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D11" s="11">
         <v>3663</v>
@@ -5470,7 +5471,7 @@
         <v>3921</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J11" s="16">
         <v>4044</v>
@@ -5487,10 +5488,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" s="11">
         <v>6063</v>
@@ -5512,7 +5513,7 @@
         <v>6685</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J12" s="16">
         <v>7466</v>
@@ -5529,10 +5530,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D13" s="11">
         <v>3345</v>
@@ -5554,7 +5555,7 @@
         <v>3580</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J13" s="16">
         <v>3693</v>
@@ -5571,10 +5572,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D14" s="11">
         <v>8879</v>
@@ -5596,7 +5597,7 @@
         <v>9501</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J14" s="24">
         <v>9803</v>
@@ -5613,10 +5614,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D15" s="11">
         <v>53839</v>
@@ -5637,7 +5638,7 @@
         <v>53883</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J15" s="24">
         <v>61612</v>
@@ -5655,10 +5656,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D16" s="11">
         <v>32675</v>
@@ -5679,7 +5680,7 @@
         <v>34278</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J16" s="16">
         <v>37540</v>
@@ -5742,10 +5743,10 @@
         <v>13</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D19" s="15">
         <v>66724</v>
@@ -5765,7 +5766,7 @@
         <v>71229</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J19" s="16">
         <v>72949</v>
@@ -5784,10 +5785,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D20" s="15">
         <v>85428</v>
@@ -5808,7 +5809,7 @@
         <v>90562</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J20" s="16">
         <v>98727</v>
@@ -5825,10 +5826,10 @@
         <v>15</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D21" s="15">
         <v>29862</v>
@@ -5849,7 +5850,7 @@
         <v>31430</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J21" s="16">
         <v>32688</v>
@@ -5866,10 +5867,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D22" s="15">
         <v>2528</v>
@@ -5891,7 +5892,7 @@
         <v>2705</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J22" s="16">
         <v>2791</v>
@@ -5908,10 +5909,10 @@
         <v>17</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D23" s="15">
         <v>10309</v>
@@ -5932,7 +5933,7 @@
         <v>10814</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J23" s="16">
         <v>11844</v>
@@ -5949,10 +5950,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D24" s="15">
         <v>54200</v>
@@ -5973,7 +5974,7 @@
         <v>56859</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J24" s="16">
         <v>62269</v>
@@ -5990,10 +5991,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D25" s="15">
         <v>27023</v>
@@ -6014,7 +6015,7 @@
         <v>27045</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J25" s="16">
         <v>30924</v>
@@ -6075,10 +6076,10 @@
         <v>20</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D28" s="15">
         <v>10374</v>
@@ -6100,7 +6101,7 @@
         <v>11100</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J28" s="16">
         <v>11454</v>
@@ -6117,10 +6118,10 @@
         <v>21</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D29" s="15">
         <v>147432</v>
@@ -6140,7 +6141,7 @@
         <v>150898</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J29" s="16">
         <v>157716</v>
@@ -6201,10 +6202,10 @@
         <v>22</v>
       </c>
       <c r="B32" s="29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D32" s="15">
         <v>22099</v>
@@ -6226,7 +6227,7 @@
         <v>24766</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J32" s="16">
         <v>27214</v>
@@ -6243,10 +6244,10 @@
         <v>23</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D33" s="15">
         <v>10790</v>
@@ -6268,7 +6269,7 @@
         <v>11722</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J33" s="16">
         <v>13287</v>
@@ -6285,10 +6286,10 @@
         <v>24</v>
       </c>
       <c r="B34" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D34" s="15">
         <v>18192</v>
@@ -6310,7 +6311,7 @@
         <v>20059</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J34" s="16">
         <v>22402</v>
@@ -6327,10 +6328,10 @@
         <v>25</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D35" s="15">
         <v>27774</v>
@@ -6352,7 +6353,7 @@
         <v>29718</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J35" s="16">
         <v>30665</v>
@@ -6413,10 +6414,10 @@
         <v>26</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D38" s="15">
         <v>9000</v>
@@ -6436,7 +6437,7 @@
         <v>9000</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J38" s="16">
         <v>9000</v>
@@ -6453,10 +6454,10 @@
         <v>27</v>
       </c>
       <c r="B39" s="29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D39" s="15">
         <v>9000</v>
@@ -6476,7 +6477,7 @@
         <v>9000</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J39" s="16">
         <v>9000</v>
@@ -6537,10 +6538,10 @@
         <v>28</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D42" s="15">
         <v>37901</v>
@@ -6562,7 +6563,7 @@
         <v>41796</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J42" s="16">
         <v>46673</v>
@@ -6579,10 +6580,10 @@
         <v>29</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D43" s="15">
         <v>57345</v>
@@ -6603,7 +6604,7 @@
         <v>58836</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J43" s="16">
         <v>65624</v>
@@ -6620,10 +6621,10 @@
         <v>30</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D44" s="15">
         <v>42203</v>
@@ -6644,7 +6645,7 @@
         <v>44621</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J44" s="16">
         <v>46197</v>
@@ -6705,10 +6706,10 @@
         <v>31</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D47" s="15">
         <v>8940</v>
@@ -6730,7 +6731,7 @@
         <v>9988</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J47" s="16">
         <v>11009</v>
@@ -6747,10 +6748,10 @@
         <v>32</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D48" s="15">
         <v>28279</v>
@@ -6772,7 +6773,7 @@
         <v>30722</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J48" s="16">
         <v>34824</v>
@@ -6789,10 +6790,10 @@
         <v>33</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D49" s="15">
         <v>16371</v>
@@ -6814,7 +6815,7 @@
         <v>18054</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J49" s="16">
         <v>20160</v>
@@ -6831,10 +6832,10 @@
         <v>34</v>
       </c>
       <c r="B50" s="29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D50" s="15">
         <v>24590</v>
@@ -6856,7 +6857,7 @@
         <v>26336</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J50" s="16">
         <v>27150</v>
@@ -6873,10 +6874,10 @@
         <v>35</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D51" s="15">
         <v>183627</v>
@@ -6897,7 +6898,7 @@
         <v>192635</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J51" s="16">
         <v>210966</v>
@@ -6914,10 +6915,10 @@
         <v>36</v>
       </c>
       <c r="B52" s="29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D52" s="15">
         <v>22512</v>
@@ -6938,7 +6939,7 @@
         <v>22531</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J52" s="16">
         <v>25762</v>
@@ -6984,37 +6985,37 @@
       <c r="O53" s="30"/>
     </row>
     <row r="54" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A54" s="198" t="str">
+      <c r="A54" s="167" t="str">
         <f>+A1</f>
         <v>DIAGO CO-OPERATIVE HOUSING SOCIETY LIMITED</v>
       </c>
-      <c r="B54" s="199"/>
-      <c r="C54" s="199"/>
-      <c r="D54" s="199"/>
-      <c r="E54" s="199"/>
-      <c r="F54" s="199"/>
-      <c r="G54" s="199"/>
-      <c r="H54" s="199"/>
-      <c r="I54" s="199"/>
-      <c r="J54" s="199"/>
-      <c r="K54" s="199"/>
-      <c r="L54" s="199"/>
+      <c r="B54" s="168"/>
+      <c r="C54" s="168"/>
+      <c r="D54" s="168"/>
+      <c r="E54" s="168"/>
+      <c r="F54" s="168"/>
+      <c r="G54" s="168"/>
+      <c r="H54" s="168"/>
+      <c r="I54" s="168"/>
+      <c r="J54" s="168"/>
+      <c r="K54" s="168"/>
+      <c r="L54" s="168"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="200" t="s">
-        <v>269</v>
-      </c>
-      <c r="B55" s="200"/>
-      <c r="C55" s="200"/>
-      <c r="D55" s="200"/>
-      <c r="E55" s="200"/>
-      <c r="F55" s="200"/>
-      <c r="G55" s="200"/>
-      <c r="H55" s="200"/>
-      <c r="I55" s="200"/>
-      <c r="J55" s="200"/>
-      <c r="K55" s="200"/>
-      <c r="L55" s="200"/>
+      <c r="A55" s="169" t="s">
+        <v>268</v>
+      </c>
+      <c r="B55" s="169"/>
+      <c r="C55" s="169"/>
+      <c r="D55" s="169"/>
+      <c r="E55" s="169"/>
+      <c r="F55" s="169"/>
+      <c r="G55" s="169"/>
+      <c r="H55" s="169"/>
+      <c r="I55" s="169"/>
+      <c r="J55" s="169"/>
+      <c r="K55" s="169"/>
+      <c r="L55" s="169"/>
     </row>
     <row r="56" spans="1:15" s="27" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="26" t="s">
@@ -7030,10 +7031,10 @@
         <v>13</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>63</v>
@@ -7070,10 +7071,10 @@
         <v>37</v>
       </c>
       <c r="B58" s="29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D58" s="15">
         <v>8000</v>
@@ -7093,7 +7094,7 @@
         <v>8000</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J58" s="16">
         <v>8000</v>
@@ -7110,10 +7111,10 @@
         <v>38</v>
       </c>
       <c r="B59" s="29" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D59" s="15">
         <v>4000</v>
@@ -7133,7 +7134,7 @@
         <v>4000</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J59" s="16">
         <v>4000</v>
@@ -7150,10 +7151,10 @@
         <v>39</v>
       </c>
       <c r="B60" s="29" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D60" s="15">
         <v>6000</v>
@@ -7173,7 +7174,7 @@
         <v>6000</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J60" s="16">
         <v>6000</v>
@@ -7190,10 +7191,10 @@
         <v>40</v>
       </c>
       <c r="B61" s="29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D61" s="15">
         <v>6000</v>
@@ -7213,7 +7214,7 @@
         <v>6000</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J61" s="16">
         <v>6000</v>
@@ -7260,7 +7261,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B63" s="28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D63" s="13"/>
       <c r="E63" s="14"/>
@@ -7274,10 +7275,10 @@
         <v>41</v>
       </c>
       <c r="B64" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D64" s="15">
         <v>49178</v>
@@ -7299,7 +7300,7 @@
         <v>52670</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J64" s="16">
         <v>54297</v>
@@ -7316,10 +7317,10 @@
         <v>42</v>
       </c>
       <c r="B65" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D65" s="15">
         <v>93940</v>
@@ -7340,7 +7341,7 @@
         <v>98873</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J65" s="16">
         <v>102831</v>
@@ -7357,10 +7358,10 @@
         <v>43</v>
       </c>
       <c r="B66" s="29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D66" s="15">
         <v>1355</v>
@@ -7380,7 +7381,7 @@
         <v>1356</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J66" s="16">
         <v>1551</v>
@@ -7428,7 +7429,7 @@
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="32"/>
       <c r="B68" s="28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D68" s="13"/>
       <c r="E68" s="14"/>
@@ -7442,10 +7443,10 @@
         <v>44</v>
       </c>
       <c r="B69" s="29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D69" s="15">
         <v>26753</v>
@@ -7467,7 +7468,7 @@
         <v>28653</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J69" s="16">
         <v>29538</v>
@@ -7484,10 +7485,10 @@
         <v>45</v>
       </c>
       <c r="B70" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D70" s="15">
         <v>4698</v>
@@ -7508,7 +7509,7 @@
         <v>4945</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J70" s="16">
         <v>5086</v>
@@ -7525,10 +7526,10 @@
         <v>46</v>
       </c>
       <c r="B71" s="29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D71" s="15">
         <v>4496</v>
@@ -7550,7 +7551,7 @@
         <v>4810</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J71" s="16">
         <v>4964</v>
@@ -7567,10 +7568,10 @@
         <v>47</v>
       </c>
       <c r="B72" s="29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D72" s="15">
         <v>4539</v>
@@ -7591,7 +7592,7 @@
         <v>4542</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J72" s="16">
         <v>5194</v>
@@ -7638,7 +7639,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B74" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D74" s="23"/>
       <c r="E74" s="23"/>
@@ -7653,10 +7654,10 @@
         <v>48</v>
       </c>
       <c r="B75" s="29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D75" s="15">
         <v>36411</v>
@@ -7677,7 +7678,7 @@
         <v>38198</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J75" s="4">
         <v>41832</v>
@@ -7694,10 +7695,10 @@
         <v>49</v>
       </c>
       <c r="B76" s="29" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D76" s="15">
         <v>77127</v>
@@ -7718,7 +7719,7 @@
         <v>77190</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J76" s="4">
         <v>88262</v>
@@ -7765,7 +7766,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B78" s="28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="23"/>
@@ -7780,10 +7781,10 @@
         <v>50</v>
       </c>
       <c r="B79" s="29" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D79" s="15">
         <v>54400</v>
@@ -7804,7 +7805,7 @@
         <v>57068</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J79" s="4">
         <v>62499</v>
@@ -7928,7 +7929,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="203" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B2" s="203"/>
       <c r="C2" s="203"/>
@@ -7943,25 +7944,25 @@
         <v>94</v>
       </c>
       <c r="B3" s="141" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="141" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="141" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="142" t="s">
+        <v>240</v>
+      </c>
+      <c r="F3" s="141" t="s">
+        <v>241</v>
+      </c>
+      <c r="G3" s="142" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="141" t="s">
-        <v>240</v>
-      </c>
-      <c r="D3" s="141" t="s">
-        <v>273</v>
-      </c>
-      <c r="E3" s="142" t="s">
-        <v>241</v>
-      </c>
-      <c r="F3" s="141" t="s">
+      <c r="H3" s="141" t="s">
         <v>242</v>
-      </c>
-      <c r="G3" s="142" t="s">
-        <v>129</v>
-      </c>
-      <c r="H3" s="141" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -7995,7 +7996,7 @@
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="136" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B5" s="10">
         <v>0</v>
@@ -8024,7 +8025,7 @@
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="136" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B6" s="10">
         <v>0</v>
@@ -8053,7 +8054,7 @@
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="136" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B7" s="10">
         <v>0.1</v>
@@ -8082,7 +8083,7 @@
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="136" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B8" s="10">
         <v>0.15</v>
@@ -8111,7 +8112,7 @@
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="136" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B9" s="10">
         <v>0.15</v>
@@ -8140,7 +8141,7 @@
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="137" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B10" s="138"/>
       <c r="C10" s="121">
@@ -8225,26 +8226,26 @@
       <c r="J1" s="208"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="175" t="s">
+      <c r="A2" s="179" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2" s="179"/>
+      <c r="C2" s="179"/>
+      <c r="D2" s="179"/>
+      <c r="E2" s="179"/>
+      <c r="G2" s="179" t="s">
         <v>244</v>
       </c>
-      <c r="B2" s="175"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="G2" s="175" t="s">
-        <v>245</v>
-      </c>
-      <c r="H2" s="175"/>
-      <c r="I2" s="175"/>
-      <c r="J2" s="175"/>
+      <c r="H2" s="179"/>
+      <c r="I2" s="179"/>
+      <c r="J2" s="179"/>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="154" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B3" s="154" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3" s="154" t="s">
         <v>32</v>
@@ -8262,7 +8263,7 @@
         <v>106</v>
       </c>
       <c r="I3" s="154" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J3" s="154" t="s">
         <v>109</v>
@@ -8276,10 +8277,10 @@
         <v>30</v>
       </c>
       <c r="C4" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="151" t="s">
         <v>179</v>
-      </c>
-      <c r="D4" s="151" t="s">
-        <v>180</v>
       </c>
       <c r="E4" s="153">
         <f>6912-2930</f>
@@ -8327,7 +8328,7 @@
         <v>3</v>
       </c>
       <c r="H6" s="145" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I6" s="146" t="s">
         <v>38</v>
@@ -8338,7 +8339,7 @@
     </row>
     <row r="7" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="204" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -8348,7 +8349,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="145" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I7" s="146" t="s">
         <v>51</v>
@@ -8360,10 +8361,10 @@
     </row>
     <row r="8" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="154" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B8" s="154" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C8" s="154" t="s">
         <v>32</v>
@@ -8396,7 +8397,7 @@
         <v>102</v>
       </c>
       <c r="D9" s="155" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E9" s="156">
         <v>10883</v>
@@ -8414,7 +8415,7 @@
         <v>303</v>
       </c>
       <c r="D10" s="145" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10" s="147">
         <v>8989</v>
@@ -8433,7 +8434,7 @@
         <v>402</v>
       </c>
       <c r="D11" s="145" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E11" s="147">
         <v>1511</v>
@@ -8461,7 +8462,7 @@
     </row>
     <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="204" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B14" s="204"/>
       <c r="C14" s="204"/>
@@ -8472,10 +8473,10 @@
     </row>
     <row r="15" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="154" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B15" s="154" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C15" s="154" t="s">
         <v>32</v>
@@ -8500,7 +8501,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="155" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E16" s="156">
         <v>2000</v>
@@ -8513,13 +8514,13 @@
         <v>2</v>
       </c>
       <c r="B17" s="143" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C17" s="143">
         <v>1</v>
       </c>
       <c r="D17" s="145" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E17" s="147">
         <v>2000</v>
@@ -8537,7 +8538,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="145" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E18" s="147">
         <v>2000</v>
@@ -8555,7 +8556,7 @@
         <v>101</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E19" s="147">
         <v>2000</v>
@@ -8572,7 +8573,7 @@
         <v>102</v>
       </c>
       <c r="D20" s="145" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E20" s="147">
         <v>2000</v>
@@ -8589,7 +8590,7 @@
         <v>202</v>
       </c>
       <c r="D21" s="145" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E21" s="147">
         <v>2000</v>
@@ -8606,7 +8607,7 @@
         <v>203</v>
       </c>
       <c r="D22" s="145" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E22" s="147">
         <v>2000</v>
@@ -8623,7 +8624,7 @@
         <v>301</v>
       </c>
       <c r="D23" s="145" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E23" s="147">
         <v>2000</v>
@@ -8640,7 +8641,7 @@
         <v>301</v>
       </c>
       <c r="D24" s="145" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E24" s="147">
         <v>2000</v>
@@ -8657,7 +8658,7 @@
         <v>303</v>
       </c>
       <c r="D25" s="145" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E25" s="147">
         <v>2000</v>
@@ -8674,7 +8675,7 @@
         <v>303</v>
       </c>
       <c r="D26" s="145" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E26" s="147">
         <v>2000</v>
@@ -8691,7 +8692,7 @@
         <v>403</v>
       </c>
       <c r="D27" s="145" t="s">
-        <v>112</v>
+        <v>300</v>
       </c>
       <c r="E27" s="147">
         <v>2000</v>
